--- a/docs/external/dist/Concord-Financial-Model.xlsx
+++ b/docs/external/dist/Concord-Financial-Model.xlsx
@@ -62,7 +62,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -84,11 +84,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -113,6 +157,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1851,7 +1897,6 @@
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1863,7 +1908,6 @@
         <f>B4*'플랜·마진표'!B5</f>
         <v/>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -2094,15 +2138,15 @@
           <t>파일럿 믹스 (650,000원 · 14h)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="21" t="n"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>8플랜 평균 (707,500원 · 15h)</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2486,28 +2530,28 @@
           <t>보수</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="21" t="n"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="21" t="n"/>
       <c r="M13" s="3" t="inlineStr">
         <is>
           <t>공격</t>
         </is>
       </c>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
+      <c r="N13" s="20" t="n"/>
+      <c r="O13" s="20" t="n"/>
+      <c r="P13" s="20" t="n"/>
+      <c r="Q13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -5197,7 +5241,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>주: 반기말 활성 학생은 소스 문서 확정 앵커, 월별은 선형 보간. 누적액은 월별 적산값으로 소스 요약의 반올림 근사(기본 약 15.0억·5.1억)와 다를 수 있다.</t>
+          <t>주: 반기말 활성 학생은 소스 문서 확정 앵커, 월별은 선형 보간. 3년 누적은 월별 적산값 — 2026-07-14부로 전 대외 문서가 이 기준으로 통일됨 (기본 약 19.1억·6.3억).</t>
         </is>
       </c>
     </row>
